--- a/Paper/_statistics/baselines/monthly.xlsx
+++ b/Paper/_statistics/baselines/monthly.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benel\Coding\Python\Paper\_statistics\baselines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A1073FC-08F6-4092-9079-B0E1B26A1AC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF9F59E-505F-493A-B218-D4A50A34CC1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="50724" yWindow="6240" windowWidth="17280" windowHeight="9960" xr2:uid="{B0CDCC7D-8E54-4447-A130-B70C09A1847F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B0CDCC7D-8E54-4447-A130-B70C09A1847F}"/>
   </bookViews>
   <sheets>
     <sheet name="table_1" sheetId="1" r:id="rId1"/>
-    <sheet name="table_2_new" sheetId="6" r:id="rId2"/>
+    <sheet name="table_2" sheetId="6" r:id="rId2"/>
     <sheet name="crises_vs_mcap" sheetId="3" r:id="rId3"/>
     <sheet name="crises_raw" sheetId="4" r:id="rId4"/>
   </sheets>
@@ -1024,18 +1024,18 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1059,7 +1059,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2990,6 +2990,184 @@
       </border>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -3023,184 +3201,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDDEBF7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDDEBF7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDDEBF7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDDEBF7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDDEBF7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDDEBF7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDDEBF7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDDEBF7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDDEBF7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDDEBF7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDDEBF7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDDEBF7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3215,7 +3215,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{72710322-2B29-421F-B682-2C9EF37F16B1}" name="Table2" displayName="Table2" ref="A1:X8" totalsRowShown="0" headerRowDxfId="105" dataDxfId="106" headerRowBorderDxfId="125" tableBorderDxfId="126">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{72710322-2B29-421F-B682-2C9EF37F16B1}" name="Table2" displayName="Table2" ref="A1:X8" totalsRowShown="0" headerRowDxfId="126" dataDxfId="124" headerRowBorderDxfId="125" tableBorderDxfId="123">
   <autoFilter ref="A1:X8" xr:uid="{72710322-2B29-421F-B682-2C9EF37F16B1}"/>
   <tableColumns count="24">
     <tableColumn id="1" xr3:uid="{A46C3251-E5BB-489B-89DA-BE1E07FF63B3}" name="model"/>
@@ -3224,24 +3224,24 @@
     <tableColumn id="4" xr3:uid="{F6C45E6C-F150-4BA8-A01E-B06DB01905CA}" name="role"/>
     <tableColumn id="5" xr3:uid="{869990E4-767F-4CEE-B713-1D3EDF1E6BA0}" name="detector"/>
     <tableColumn id="8" xr3:uid="{F7589F13-3854-47F7-A25D-165AB1B89AD0}" name="base_run"/>
-    <tableColumn id="10" xr3:uid="{B037FC52-AD34-4740-99C7-E1492824C3D6}" name="full_cum_return" dataDxfId="124"/>
-    <tableColumn id="11" xr3:uid="{FF230FA4-3751-4FE6-8704-51E4DF698A49}" name="full_cagr" dataDxfId="123"/>
-    <tableColumn id="12" xr3:uid="{C2BA2444-E448-4C68-8FB4-B5505628C674}" name="full_ann_vol" dataDxfId="122"/>
-    <tableColumn id="13" xr3:uid="{0C827673-F756-4B72-9060-7E69CC62A589}" name="full_sharpe" dataDxfId="121"/>
-    <tableColumn id="14" xr3:uid="{047FDFD2-5896-4551-8E34-CFEA78334870}" name="full_sortino" dataDxfId="120"/>
-    <tableColumn id="15" xr3:uid="{C2261618-EA2F-497B-A2B1-79E7F0B69ABC}" name="full_calmar" dataDxfId="119"/>
-    <tableColumn id="16" xr3:uid="{6C3C581E-57A0-4E03-A055-05AF6EB42C5A}" name="full_max_dd" dataDxfId="118"/>
-    <tableColumn id="17" xr3:uid="{25471F10-D389-421D-9AE8-A1C9450DD42C}" name="full_ulcer" dataDxfId="117"/>
-    <tableColumn id="18" xr3:uid="{3F0634A8-BEFE-43A1-A5CD-A4719AE3899A}" name="full_turnover_pa" dataDxfId="116"/>
-    <tableColumn id="19" xr3:uid="{B9D92813-033C-475C-BACC-0DAC70E52E31}" name="ret_outside_crises_ann" dataDxfId="115"/>
-    <tableColumn id="20" xr3:uid="{2F063AD3-1753-40CE-8A32-C473CFC4D1E9}" name="sharpe_outside_crises" dataDxfId="114"/>
-    <tableColumn id="21" xr3:uid="{B017B14B-1D3F-4184-B71B-167E683637E0}" name="sharpe_inside_crises" dataDxfId="113"/>
-    <tableColumn id="29" xr3:uid="{B9ABC6E7-8A2F-42F5-92F0-8E7F91E2DB05}" name="fix_hit_count_full" dataDxfId="112"/>
-    <tableColumn id="30" xr3:uid="{CD802DD5-6E31-48F7-997C-06A26859C68A}" name="fix_hit_count_ptt" dataDxfId="111"/>
-    <tableColumn id="31" xr3:uid="{954CC678-020A-4CD5-B732-50B7D3204F20}" name="fix_hit_count_ttp" dataDxfId="110"/>
-    <tableColumn id="32" xr3:uid="{A45332DE-A539-483C-BE1B-D97B169E7AFC}" name="flex_hit_count_full" dataDxfId="109"/>
-    <tableColumn id="33" xr3:uid="{BD4F0E9A-FFE3-4DC6-9DA3-B222AB8DF58D}" name="flex_hit_count_ptt" dataDxfId="108"/>
-    <tableColumn id="34" xr3:uid="{BC186E60-AD2E-44DC-B02A-FFD63DD56258}" name="flex_hit_count_ttp" dataDxfId="107"/>
+    <tableColumn id="10" xr3:uid="{B037FC52-AD34-4740-99C7-E1492824C3D6}" name="full_cum_return" dataDxfId="122"/>
+    <tableColumn id="11" xr3:uid="{FF230FA4-3751-4FE6-8704-51E4DF698A49}" name="full_cagr" dataDxfId="121"/>
+    <tableColumn id="12" xr3:uid="{C2BA2444-E448-4C68-8FB4-B5505628C674}" name="full_ann_vol" dataDxfId="120"/>
+    <tableColumn id="13" xr3:uid="{0C827673-F756-4B72-9060-7E69CC62A589}" name="full_sharpe" dataDxfId="119"/>
+    <tableColumn id="14" xr3:uid="{047FDFD2-5896-4551-8E34-CFEA78334870}" name="full_sortino" dataDxfId="118"/>
+    <tableColumn id="15" xr3:uid="{C2261618-EA2F-497B-A2B1-79E7F0B69ABC}" name="full_calmar" dataDxfId="117"/>
+    <tableColumn id="16" xr3:uid="{6C3C581E-57A0-4E03-A055-05AF6EB42C5A}" name="full_max_dd" dataDxfId="116"/>
+    <tableColumn id="17" xr3:uid="{25471F10-D389-421D-9AE8-A1C9450DD42C}" name="full_ulcer" dataDxfId="115"/>
+    <tableColumn id="18" xr3:uid="{3F0634A8-BEFE-43A1-A5CD-A4719AE3899A}" name="full_turnover_pa" dataDxfId="114"/>
+    <tableColumn id="19" xr3:uid="{B9D92813-033C-475C-BACC-0DAC70E52E31}" name="ret_outside_crises_ann" dataDxfId="113"/>
+    <tableColumn id="20" xr3:uid="{2F063AD3-1753-40CE-8A32-C473CFC4D1E9}" name="sharpe_outside_crises" dataDxfId="112"/>
+    <tableColumn id="21" xr3:uid="{B017B14B-1D3F-4184-B71B-167E683637E0}" name="sharpe_inside_crises" dataDxfId="111"/>
+    <tableColumn id="29" xr3:uid="{B9ABC6E7-8A2F-42F5-92F0-8E7F91E2DB05}" name="fix_hit_count_full" dataDxfId="110"/>
+    <tableColumn id="30" xr3:uid="{CD802DD5-6E31-48F7-997C-06A26859C68A}" name="fix_hit_count_ptt" dataDxfId="109"/>
+    <tableColumn id="31" xr3:uid="{954CC678-020A-4CD5-B732-50B7D3204F20}" name="fix_hit_count_ttp" dataDxfId="108"/>
+    <tableColumn id="32" xr3:uid="{A45332DE-A539-483C-BE1B-D97B169E7AFC}" name="flex_hit_count_full" dataDxfId="107"/>
+    <tableColumn id="33" xr3:uid="{BD4F0E9A-FFE3-4DC6-9DA3-B222AB8DF58D}" name="flex_hit_count_ptt" dataDxfId="106"/>
+    <tableColumn id="34" xr3:uid="{BC186E60-AD2E-44DC-B02A-FFD63DD56258}" name="flex_hit_count_ttp" dataDxfId="105"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
